--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,107 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128621286</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91653</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Halåbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012342</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91653</v>
+        <v>91659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91659</v>
+        <v>91665</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91665</v>
+        <v>91667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91667</v>
+        <v>91668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91668</v>
+        <v>91695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91695</v>
+        <v>91700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91700</v>
+        <v>91705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>91709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91709</v>
+        <v>91714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91716</v>
+        <v>91721</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>128621286</v>
       </c>
       <c r="B5" t="n">
-        <v>91721</v>
+        <v>91727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104022828</v>
+        <v>128621286</v>
       </c>
       <c r="B2" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fyrprickmyran, Jmt</t>
+          <t>Halåbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571451.1619288391</v>
+        <v>571500</v>
       </c>
       <c r="R2" t="n">
-        <v>7012286.815210903</v>
+        <v>7012342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,66 +760,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104022821</v>
+        <v>104022832</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fyrprickmyran, Jmt</t>
+          <t>Vinkelmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571445.4246920757</v>
+        <v>571628</v>
       </c>
       <c r="R3" t="n">
-        <v>7012280.826096042</v>
+        <v>7012131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,11 +867,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,50 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104022832</v>
+        <v>128621284</v>
       </c>
       <c r="B4" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vinkelmyran, Jmt</t>
+          <t>Halåbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571628.4627294317</v>
+        <v>571431</v>
       </c>
       <c r="R4" t="n">
-        <v>7012131.120043688</v>
+        <v>7012280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,61 +972,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128621286</v>
+        <v>104022821</v>
       </c>
       <c r="B5" t="n">
-        <v>91727</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halåbodarna, Jmt</t>
+          <t>Fyrprickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571500</v>
+        <v>571446</v>
       </c>
       <c r="R5" t="n">
-        <v>7012342</v>
+        <v>7012281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,12 +1053,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,21 +1079,586 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128800699</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571663</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012552</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128800700</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sörbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571558</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012375</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128800702</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sörbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571654</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7012417</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104022828</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fyrprickmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>571451</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7012287</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104022827</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fyrprickmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571420</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7012413</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 32903-2024 artfynd.xlsx
+++ b/artfynd/A 32903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621286</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022832</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128621284</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800699</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800700</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800702</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022828</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,8 +1706,24 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>